--- a/sample_data/sample_orders.xlsx
+++ b/sample_data/sample_orders.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bright Medical Trading Ltd</t>
+          <t>Victoria Harbour Eye Institute</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,16 +498,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MED-LENS-001</t>
+          <t>VIS-SLIT-001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Optical Lens Kit</t>
+          <t>Slit Lamp Examination Unit</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>46218</v>
@@ -539,29 +539,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Silver Oak Supplies</t>
+          <t>Pearl River Medical Distribution Co</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Guangdong</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MED-GLOVE-002</t>
+          <t>VIS-LENS-002</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nitrile Exam Gloves (Box of 100)</t>
+          <t>Trial Lens Set (Standard)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15 days</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -586,33 +586,33 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tai Yick Trading Co</t>
+          <t>Huangpu District Eye Hospital</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MED-MASK-003</t>
+          <t>CONS-WIPE-009</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Surgical Face Mask (Box of 50)</t>
+          <t>Lens Cleaning Wipes (Pack of 200)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46215</v>
+        <v>46213</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -621,12 +621,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>15 days</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Marcus</t>
         </is>
       </c>
     </row>
@@ -641,26 +641,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Formosa Industrial Group</t>
+          <t>Kowloon Central Hospital</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IND-VALVE-004</t>
+          <t>DIAG-TONO-007</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Industrial Pressure Valve</t>
+          <t>Non-Contact Tonometer</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>46223</v>
@@ -672,12 +672,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45 days</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Jesse</t>
         </is>
       </c>
     </row>
@@ -688,47 +688,47 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bright Medical Trading Ltd</t>
+          <t>Beijing Capital Eye Center</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IND-PUMP-005</t>
+          <t>DIAG-OCT-005</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Unit</t>
+          <t>Handheld OCT Scanner</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46228</v>
+        <v>46225</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>45 days</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Priya</t>
         </is>
       </c>
     </row>
@@ -739,33 +739,33 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Golden Harbor Logistics</t>
+          <t>Golden Bay Optical Chain</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Guangdong</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OFF-CHAIR-006</t>
+          <t>CONS-DROP-010</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ergonomic Office Chair</t>
+          <t>Diagnostic Dilation Drops (Box of 50)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46221</v>
+        <v>46217</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -790,33 +790,33 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lion City Retail Pte Ltd</t>
+          <t>Lion Rock Vision Clinic Group</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OFF-DESK-007</t>
+          <t>CONS-CALSTRIP-012</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adjustable Standing Desk</t>
+          <t>Calibration Test Strips (Box of 100)</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46222</v>
+        <v>46219</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -841,84 +841,84 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Silver Oak Supplies</t>
+          <t>Shanghai Vision Research Institute</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MED-LENS-001</t>
+          <t>VIS-REFR-003</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Optical Lens Kit</t>
+          <t>Digital Refractor Head</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46217</v>
+        <v>46228</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15 days</t>
+          <t>45 days</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Priya</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SO-2026-005</t>
+          <t>SO-2026-009</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46208</v>
+        <v>46206</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Formosa Industrial Group</t>
+          <t>Chaoyang Medical Equipment Co</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MED-GLOVE-002</t>
+          <t>DIAG-AUTO-008</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nitrile Exam Gloves (Box of 100)</t>
+          <t>Auto Lensmeter</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46224</v>
+        <v>46221</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -932,22 +932,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Jesse</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SO-2026-009</t>
+          <t>SO-2026-010</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46208</v>
+        <v>46207</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tai Yick Trading Co</t>
+          <t>Harbour City Biomedical Services</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -957,23 +957,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MED-LENS-999</t>
+          <t>PART-BULB-013</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Optical Lens Kit (Discontinued Variant)</t>
+          <t>Slit Lamp Replacement Bulb</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46225</v>
+        <v>46220</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -983,48 +983,48 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Wendy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SO-2026-010</t>
+          <t>SO-2026-011</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Golden Harbor Logistics</t>
+          <t>Northern Star University Hospital</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IND-VALVE-004</t>
+          <t>PART-CHINREST-014</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Industrial Pressure Valve</t>
+          <t>Chin Rest Assembly (Replacement)</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46219</v>
+        <v>46222</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1034,58 +1034,1268 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Marcus</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SO-2026-011</t>
+          <t>SO-2026-012</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New Territories Optical Supplies</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VIS-LENS-002</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trial Lens Set (Standard)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SO-2026-013</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Zhuhai Cross-Border Medical Center</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Guangdong</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CONS-WIPE-009</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lens Cleaning Wipes (Pack of 200)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>80</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15 days</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SO-2026-014</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bund Optical Partners</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DIAG-FUND-006</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fundus Camera Unit</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SO-2026-015</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sichuan Regional Health Distributors</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Other Mainland China</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CONS-COVER-011</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Disposable Chin Rest Covers (Pack of 500)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SO-2026-016</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Lion City Retail Pte Ltd</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MED-MASK-003</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Surgical Face Mask (Box of 50)</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yangtze Vision Clinic Network</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Other Mainland China</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>VIS-SLIT-001</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Slit Lamp Examination Unit</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SO-2026-017</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Fujian Coastal Eye Care Group</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Other Mainland China</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DIAG-TONO-007</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Non-Contact Tonometer</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>45 days</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SO-2026-018</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Victoria Harbour Eye Institute</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CONS-DROP-010</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diagnostic Dilation Drops (Box of 50)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SO-2026-019</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pearl River Medical Distribution Co</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Guangdong</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PART-CAL-015</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tonometer Calibration Kit</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SO-2026-020</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Huangpu District Eye Hospital</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CONS-CALSTRIP-012</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Calibration Test Strips (Box of 100)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>15 days</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SO-2026-021</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kowloon Central Hospital</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>VIS-LENS-002</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Trial Lens Set (Standard)</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SO-2026-022</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Beijing Capital Eye Center</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DIAG-AUTO-008</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Auto Lensmeter</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SO-2026-023</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lion Rock Vision Clinic Group</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PART-BULB-013</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Slit Lamp Replacement Bulb</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SO-2026-024</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Golden Bay Optical Chain</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Guangdong</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>VIS-REFR-003</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Digital Refractor Head</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>45 days</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SO-2026-025</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chaoyang Medical Equipment Co</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CONS-WIPE-009</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lens Cleaning Wipes (Pack of 200)</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>60</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>15 days</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SO-2026-026</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Harbour City Biomedical Services</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PART-CHINREST-014</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Chin Rest Assembly (Replacement)</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SO-2026-027</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Shanghai Vision Research Institute</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DIAG-OCT-005</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Handheld OCT Scanner</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>45 days</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SO-2026-028</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Northern Star University Hospital</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CONS-COVER-011</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Disposable Chin Rest Covers (Pack of 500)</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
         <v>40</v>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>30 days</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="H29" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SO-2026-029</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New Territories Optical Supplies</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DIAG-FUND-006</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fundus Camera Unit</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SO-2026-030</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Zhuhai Cross-Border Medical Center</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Guangdong</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>VIS-SCOPE-099</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Portable Slit Lamp (New Model)</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SO-2026-031</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bund Optical Partners</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VIS-LOUPE-004</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Surgical Loupe Set (Legacy)</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Marcus</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SO-2026-032</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sichuan Regional Health Distributors</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Other Mainland China</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Jesse</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SO-2026-033</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yangtze Vision Clinic Network</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Other Mainland China</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CONS-WIPE-009</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lens Cleaning Wipes (Pack of 200)</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SO-2026-034</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Fujian Coastal Eye Care Group</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Other Mainland China</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CONS-DROP-010</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Diagnostic Dilation Drops (Box of 50)</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Urgent</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Wendy</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SO-2026-035</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Victoria Harbour Eye Institute</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>VIS-SLIT-001</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Slit Lamp Examination Unit</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H36" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SO-2026-010</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Pearl River Medical Distribution Co</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Guangdong</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DIAG-TONO-007</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Non-Contact Tonometer</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Priya</t>
         </is>
       </c>
     </row>
